--- a/data/data1.xlsx
+++ b/data/data1.xlsx
@@ -899,7 +899,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -908,12 +908,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1454,166 +1448,166 @@
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5" t="b">
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5" t="s">
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
     </row>
     <row r="8" ht="21.6" spans="1:18">
-      <c r="A8" s="5">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="6" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5" t="b">
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/data1.xlsx
+++ b/data/data1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29868" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="10.8" outlineLevelRow="7"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="3"/>
@@ -1473,12 +1473,12 @@
         </is>
       </c>
       <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>{"username":"jay", "password": "123456"}</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -1498,7 +1498,9 @@
         </is>
       </c>
       <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n"/>
+      <c r="R6" s="3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1552,7 +1554,9 @@
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
       <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
+      <c r="R7" s="3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="21.6" customHeight="1" s="5">
       <c r="A8" s="3" t="n">
@@ -1593,7 +1597,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>{"file": ("1.jpg", open(r"F:\software_learn\python\mihayo_learn\file\1.jpg", "rb"), "jpg")}</t>
+          <t>{"file": ("1.jpg", open("./file/1.jpg", "rb"), "jpg")}</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1619,6 +1623,304 @@
         <is>
           <t>{"file": ("1.jpg", open(r"F:\software_learn\python\mihayo_learn\file\1.jpg", "rb"), "jpg")}</t>
         </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>登录失败</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>管理员登录密码错误</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>{"username": "admin", "password": "wrong"}</t>
+        </is>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>$..meg</t>
+        </is>
+      </c>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t>用户名或密码错误</t>
+        </is>
+      </c>
+      <c r="R10" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>登录失败</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>不存在的用户登录失败</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>{"username": "nobody", "password": "123456"}</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>$..meg</t>
+        </is>
+      </c>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>用户名或密码错误</t>
+        </is>
+      </c>
+      <c r="R11" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>查询失败</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>使用无效token查询用户列表失败</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>get</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>/users</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>{"Authorization": "invalid-token-xxx"}</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>{"pagenum": 1, "pagesize": 1}</t>
+        </is>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
+        <is>
+          <t>$..meg</t>
+        </is>
+      </c>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>无效token</t>
+        </is>
+      </c>
+      <c r="R12" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>添加失败</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>缺少密码创建用户失败</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>/users</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{TOKEN}}"}</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>{"username": "no_pass"}</t>
+        </is>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t>$..meg</t>
+        </is>
+      </c>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>参数错误</t>
+        </is>
+      </c>
+      <c r="R13" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>用户管理</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>修改失败</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>修改不存在的用户状态失败</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>put</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>/users/99999/state/true</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>{"Authorization": "{{TOKEN}}"}</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>$..meg</t>
+        </is>
+      </c>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>用户不存在</t>
+        </is>
+      </c>
+      <c r="R14" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>图片上传</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>上传失败</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>未登录状态上传图片失败</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>/upload</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>{"file": ("1.jpg", open("./file/1.jpg", "rb"), "jpg")}</t>
+        </is>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t>$..meg</t>
+        </is>
+      </c>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>无效token</t>
+        </is>
+      </c>
+      <c r="R15" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
